--- a/codigos_ergopyme_homologacion.xlsx
+++ b/codigos_ergopyme_homologacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\accuv\suite_logistica\Documentos Pruebas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DD3959-CEA3-4C69-AF6C-E94F8299BD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9126A0-71BF-4F7A-AB56-21ED1DFABC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9C1AEFE4-8AB7-47ED-982D-F3E453D636C7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6431" uniqueCount="2774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6491" uniqueCount="2774">
   <si>
     <t>ACCUVISION SPA</t>
   </si>
@@ -8759,7 +8759,7 @@
     <col min="1" max="1" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="37.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.28515625" customWidth="1"/>
+    <col min="4" max="4" width="48.42578125" customWidth="1"/>
     <col min="5" max="6" width="0" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="0" style="2" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
@@ -9646,8 +9646,8 @@
       <c r="B63" t="s">
         <v>2210</v>
       </c>
-      <c r="C63" s="2" t="e">
-        <v>#N/A</v>
+      <c r="C63" t="s">
+        <v>1277</v>
       </c>
       <c r="D63" t="s">
         <v>1277</v>
@@ -13316,8 +13316,8 @@
       <c r="A293" s="1">
         <v>7011320025</v>
       </c>
-      <c r="B293" t="e">
-        <v>#N/A</v>
+      <c r="B293" t="s">
+        <v>2215</v>
       </c>
       <c r="C293" s="2">
         <v>133005</v>
@@ -15058,8 +15058,8 @@
       <c r="A400" s="1">
         <v>40111100107</v>
       </c>
-      <c r="B400" t="e">
-        <v>#N/A</v>
+      <c r="B400" t="s">
+        <v>2215</v>
       </c>
       <c r="C400" s="2" t="str">
         <f>MID(D400,1,7)</f>
@@ -15073,8 +15073,8 @@
       <c r="A401" s="1">
         <v>40111100110</v>
       </c>
-      <c r="B401" t="e">
-        <v>#N/A</v>
+      <c r="B401" t="s">
+        <v>2215</v>
       </c>
       <c r="C401" s="2" t="str">
         <f>MID(D401,1,8)</f>
@@ -15105,8 +15105,8 @@
       <c r="A403" s="1">
         <v>40111100127</v>
       </c>
-      <c r="B403" t="e">
-        <v>#N/A</v>
+      <c r="B403" t="s">
+        <v>2215</v>
       </c>
       <c r="C403" s="2" t="str">
         <f>MID(D403,1,10)</f>
@@ -15120,8 +15120,8 @@
       <c r="A404" s="1">
         <v>40111100132</v>
       </c>
-      <c r="B404" t="e">
-        <v>#N/A</v>
+      <c r="B404" t="s">
+        <v>2215</v>
       </c>
       <c r="C404" s="2" t="str">
         <f>MID(D404,1,10)</f>
@@ -15135,8 +15135,8 @@
       <c r="A405" s="1">
         <v>40111100133</v>
       </c>
-      <c r="B405" t="e">
-        <v>#N/A</v>
+      <c r="B405" t="s">
+        <v>2215</v>
       </c>
       <c r="C405" s="2" t="str">
         <f>MID(D405,1,10)</f>
@@ -15150,8 +15150,8 @@
       <c r="A406" s="1">
         <v>40111100137</v>
       </c>
-      <c r="B406" t="e">
-        <v>#N/A</v>
+      <c r="B406" t="s">
+        <v>2215</v>
       </c>
       <c r="C406" s="2" t="str">
         <f>MID(D406,1,7)</f>
@@ -15165,8 +15165,8 @@
       <c r="A407" s="1">
         <v>40111100138</v>
       </c>
-      <c r="B407" t="e">
-        <v>#N/A</v>
+      <c r="B407" t="s">
+        <v>2215</v>
       </c>
       <c r="C407" s="2" t="str">
         <f>MID(D407,1,9)</f>
@@ -15197,8 +15197,8 @@
       <c r="A409" s="1">
         <v>40111100152</v>
       </c>
-      <c r="B409" t="e">
-        <v>#N/A</v>
+      <c r="B409" t="s">
+        <v>2215</v>
       </c>
       <c r="C409" s="2" t="str">
         <f>MID(D409,1,7)</f>
@@ -15549,8 +15549,8 @@
       <c r="A430" s="1">
         <v>40111100226</v>
       </c>
-      <c r="B430" t="e">
-        <v>#N/A</v>
+      <c r="B430" t="s">
+        <v>2215</v>
       </c>
       <c r="C430" s="2" t="str">
         <f>MID(D430,1,7)</f>
@@ -15598,8 +15598,8 @@
       <c r="A433" s="1">
         <v>40111100240</v>
       </c>
-      <c r="B433" t="e">
-        <v>#N/A</v>
+      <c r="B433" t="s">
+        <v>2215</v>
       </c>
       <c r="C433" s="2" t="str">
         <f>MID(D433,1,7)</f>
@@ -15613,8 +15613,8 @@
       <c r="A434" s="1">
         <v>40111100241</v>
       </c>
-      <c r="B434" t="e">
-        <v>#N/A</v>
+      <c r="B434" t="s">
+        <v>2215</v>
       </c>
       <c r="C434" s="2" t="str">
         <f>MID(D434,1,8)</f>
@@ -15662,8 +15662,8 @@
       <c r="A437" s="1">
         <v>40111100262</v>
       </c>
-      <c r="B437" t="e">
-        <v>#N/A</v>
+      <c r="B437" t="s">
+        <v>2215</v>
       </c>
       <c r="C437" s="2" t="str">
         <f>MID(D437,1,10)</f>
@@ -15677,8 +15677,8 @@
       <c r="A438" s="1">
         <v>40111100269</v>
       </c>
-      <c r="B438" t="e">
-        <v>#N/A</v>
+      <c r="B438" t="s">
+        <v>2215</v>
       </c>
       <c r="C438" s="2" t="str">
         <f>MID(D438,1,10)</f>
@@ -15726,8 +15726,8 @@
       <c r="A441" s="1">
         <v>40111100272</v>
       </c>
-      <c r="B441" t="e">
-        <v>#N/A</v>
+      <c r="B441" t="s">
+        <v>2215</v>
       </c>
       <c r="C441" s="2" t="str">
         <f>MID(D441,1,10)</f>
@@ -15840,8 +15840,8 @@
       <c r="A448" s="1">
         <v>40111100312</v>
       </c>
-      <c r="B448" t="e">
-        <v>#N/A</v>
+      <c r="B448" t="s">
+        <v>2215</v>
       </c>
       <c r="C448" s="2" t="str">
         <f>MID(D448,1,8)</f>
@@ -15957,8 +15957,8 @@
       <c r="A455" s="1">
         <v>40111100326</v>
       </c>
-      <c r="B455" t="e">
-        <v>#N/A</v>
+      <c r="B455" t="s">
+        <v>2215</v>
       </c>
       <c r="C455" s="2" t="str">
         <f>MID(D455,1,9)</f>
@@ -15989,8 +15989,8 @@
       <c r="A457" s="1">
         <v>40111100329</v>
       </c>
-      <c r="B457" t="e">
-        <v>#N/A</v>
+      <c r="B457" t="s">
+        <v>2215</v>
       </c>
       <c r="C457" s="2" t="str">
         <f>MID(D457,1,10)</f>
@@ -16004,8 +16004,8 @@
       <c r="A458" s="1">
         <v>40111100346</v>
       </c>
-      <c r="B458" t="e">
-        <v>#N/A</v>
+      <c r="B458" t="s">
+        <v>2215</v>
       </c>
       <c r="C458" s="2" t="str">
         <f>MID(D458,1,10)</f>
@@ -16070,8 +16070,8 @@
       <c r="A462" s="1">
         <v>40111100357</v>
       </c>
-      <c r="B462" t="e">
-        <v>#N/A</v>
+      <c r="B462" t="s">
+        <v>2215</v>
       </c>
       <c r="C462" s="2" t="str">
         <f>MID(D462,1,10)</f>
@@ -16119,8 +16119,8 @@
       <c r="A465" s="1">
         <v>40111100439</v>
       </c>
-      <c r="B465" t="e">
-        <v>#N/A</v>
+      <c r="B465" t="s">
+        <v>2215</v>
       </c>
       <c r="C465" s="2" t="str">
         <f>MID(D465,1,7)</f>
@@ -16148,8 +16148,8 @@
       <c r="A467" s="1">
         <v>40111100446</v>
       </c>
-      <c r="B467" t="e">
-        <v>#N/A</v>
+      <c r="B467" t="s">
+        <v>2215</v>
       </c>
       <c r="C467" s="2" t="str">
         <f>MID(D467,1,7)</f>
@@ -16163,8 +16163,8 @@
       <c r="A468" s="1">
         <v>40111100449</v>
       </c>
-      <c r="B468" t="e">
-        <v>#N/A</v>
+      <c r="B468" t="s">
+        <v>2215</v>
       </c>
       <c r="C468" s="2" t="str">
         <f>MID(D468,1,7)</f>
@@ -16178,8 +16178,8 @@
       <c r="A469" s="1">
         <v>40111100482</v>
       </c>
-      <c r="B469" t="e">
-        <v>#N/A</v>
+      <c r="B469" t="s">
+        <v>2215</v>
       </c>
       <c r="C469" s="2" t="str">
         <f>MID(D469,1,10)</f>
@@ -16193,8 +16193,8 @@
       <c r="A470" s="1">
         <v>40111100486</v>
       </c>
-      <c r="B470" t="e">
-        <v>#N/A</v>
+      <c r="B470" t="s">
+        <v>2215</v>
       </c>
       <c r="C470" s="2" t="str">
         <f>MID(D470,1,10)</f>
@@ -16208,8 +16208,8 @@
       <c r="A471" s="1">
         <v>40111100491</v>
       </c>
-      <c r="B471" t="e">
-        <v>#N/A</v>
+      <c r="B471" t="s">
+        <v>2215</v>
       </c>
       <c r="C471" s="2" t="str">
         <f>MID(D471,1,9)</f>
@@ -16223,8 +16223,8 @@
       <c r="A472" s="1">
         <v>40111100493</v>
       </c>
-      <c r="B472" t="e">
-        <v>#N/A</v>
+      <c r="B472" t="s">
+        <v>2215</v>
       </c>
       <c r="C472" s="2" t="str">
         <f>MID(D472,1,9)</f>
@@ -16238,8 +16238,8 @@
       <c r="A473" s="1">
         <v>40111100496</v>
       </c>
-      <c r="B473" t="e">
-        <v>#N/A</v>
+      <c r="B473" t="s">
+        <v>2215</v>
       </c>
       <c r="C473" s="2" t="str">
         <f>MID(D473,1,9)</f>
@@ -16253,8 +16253,8 @@
       <c r="A474" s="1">
         <v>40111100512</v>
       </c>
-      <c r="B474" t="e">
-        <v>#N/A</v>
+      <c r="B474" t="s">
+        <v>2215</v>
       </c>
       <c r="C474" s="2" t="str">
         <f>MID(D474,1,10)</f>
@@ -16268,8 +16268,8 @@
       <c r="A475" s="1">
         <v>40111100519</v>
       </c>
-      <c r="B475" t="e">
-        <v>#N/A</v>
+      <c r="B475" t="s">
+        <v>2215</v>
       </c>
       <c r="C475" s="2" t="str">
         <f>MID(D475,1,10)</f>
@@ -16623,8 +16623,8 @@
       <c r="A496" s="1">
         <v>40111100562</v>
       </c>
-      <c r="B496" t="e">
-        <v>#N/A</v>
+      <c r="B496" t="s">
+        <v>2215</v>
       </c>
       <c r="C496" s="2" t="str">
         <f>MID(D496,1,10)</f>
@@ -16638,8 +16638,8 @@
       <c r="A497" s="1">
         <v>40111100563</v>
       </c>
-      <c r="B497" t="e">
-        <v>#N/A</v>
+      <c r="B497" t="s">
+        <v>2215</v>
       </c>
       <c r="C497" s="2" t="str">
         <f>MID(D497,1,10)</f>
@@ -16670,8 +16670,8 @@
       <c r="A499" s="1">
         <v>40111100565</v>
       </c>
-      <c r="B499" t="e">
-        <v>#N/A</v>
+      <c r="B499" t="s">
+        <v>2215</v>
       </c>
       <c r="C499" s="2" t="str">
         <f>MID(D499,1,10)</f>
@@ -16685,8 +16685,8 @@
       <c r="A500" s="1">
         <v>40111100566</v>
       </c>
-      <c r="B500" t="e">
-        <v>#N/A</v>
+      <c r="B500" t="s">
+        <v>2215</v>
       </c>
       <c r="C500" s="2" t="str">
         <f>MID(D500,1,10)</f>
@@ -16700,8 +16700,8 @@
       <c r="A501" s="1">
         <v>40111100568</v>
       </c>
-      <c r="B501" t="e">
-        <v>#N/A</v>
+      <c r="B501" t="s">
+        <v>2215</v>
       </c>
       <c r="C501" s="2" t="str">
         <f>MID(D501,1,10)</f>
@@ -16766,8 +16766,8 @@
       <c r="A505" s="1">
         <v>40111100576</v>
       </c>
-      <c r="B505" t="e">
-        <v>#N/A</v>
+      <c r="B505" t="s">
+        <v>2215</v>
       </c>
       <c r="C505" s="2" t="str">
         <f>MID(D505,1,10)</f>
@@ -16815,8 +16815,8 @@
       <c r="A508" s="1">
         <v>40111100590</v>
       </c>
-      <c r="B508" t="e">
-        <v>#N/A</v>
+      <c r="B508" t="s">
+        <v>2215</v>
       </c>
       <c r="C508" s="2" t="str">
         <f>MID(D508,1,10)</f>
@@ -16847,8 +16847,8 @@
       <c r="A510" s="1">
         <v>40111100592</v>
       </c>
-      <c r="B510" t="e">
-        <v>#N/A</v>
+      <c r="B510" t="s">
+        <v>2215</v>
       </c>
       <c r="C510" s="2" t="str">
         <f>MID(D510,1,10)</f>
@@ -16896,8 +16896,8 @@
       <c r="A513" s="1">
         <v>40111100596</v>
       </c>
-      <c r="B513" t="e">
-        <v>#N/A</v>
+      <c r="B513" t="s">
+        <v>2215</v>
       </c>
       <c r="C513" s="2" t="str">
         <f>MID(D513,1,10)</f>
@@ -16928,8 +16928,8 @@
       <c r="A515" s="1">
         <v>40111100601</v>
       </c>
-      <c r="B515" t="e">
-        <v>#N/A</v>
+      <c r="B515" t="s">
+        <v>2215</v>
       </c>
       <c r="C515" s="2" t="str">
         <f>MID(D515,1,10)</f>
@@ -16943,8 +16943,8 @@
       <c r="A516" s="1">
         <v>40111100602</v>
       </c>
-      <c r="B516" t="e">
-        <v>#N/A</v>
+      <c r="B516" t="s">
+        <v>2215</v>
       </c>
       <c r="C516" s="2" t="str">
         <f>MID(D516,1,10)</f>
@@ -16975,8 +16975,8 @@
       <c r="A518" s="1">
         <v>40111100605</v>
       </c>
-      <c r="B518" t="e">
-        <v>#N/A</v>
+      <c r="B518" t="s">
+        <v>2215</v>
       </c>
       <c r="C518" s="2" t="str">
         <f>MID(D518,1,10)</f>
@@ -16990,8 +16990,8 @@
       <c r="A519" s="1">
         <v>40111100606</v>
       </c>
-      <c r="B519" t="e">
-        <v>#N/A</v>
+      <c r="B519" t="s">
+        <v>2215</v>
       </c>
       <c r="C519" s="2" t="str">
         <f>MID(D519,1,10)</f>
@@ -17005,8 +17005,8 @@
       <c r="A520" s="1">
         <v>40111100612</v>
       </c>
-      <c r="B520" t="e">
-        <v>#N/A</v>
+      <c r="B520" t="s">
+        <v>2215</v>
       </c>
       <c r="C520" s="2" t="str">
         <f>MID(D520,1,10)</f>
@@ -17020,8 +17020,8 @@
       <c r="A521" s="1">
         <v>40111100613</v>
       </c>
-      <c r="B521" t="e">
-        <v>#N/A</v>
+      <c r="B521" t="s">
+        <v>2215</v>
       </c>
       <c r="C521" s="2" t="str">
         <f>MID(D521,1,10)</f>
@@ -17035,8 +17035,8 @@
       <c r="A522" s="1">
         <v>40111100614</v>
       </c>
-      <c r="B522" t="e">
-        <v>#N/A</v>
+      <c r="B522" t="s">
+        <v>2215</v>
       </c>
       <c r="C522" s="2" t="str">
         <f>MID(D522,1,10)</f>
@@ -17084,8 +17084,8 @@
       <c r="A525" s="1">
         <v>40111100618</v>
       </c>
-      <c r="B525" t="e">
-        <v>#N/A</v>
+      <c r="B525" t="s">
+        <v>2215</v>
       </c>
       <c r="C525" s="2" t="str">
         <f>MID(D525,1,10)</f>
@@ -17099,8 +17099,8 @@
       <c r="A526" s="1">
         <v>40111100619</v>
       </c>
-      <c r="B526" t="e">
-        <v>#N/A</v>
+      <c r="B526" t="s">
+        <v>2215</v>
       </c>
       <c r="C526" s="2" t="str">
         <f>MID(D526,1,10)</f>
@@ -17131,8 +17131,8 @@
       <c r="A528" s="1">
         <v>40111100621</v>
       </c>
-      <c r="B528" t="e">
-        <v>#N/A</v>
+      <c r="B528" t="s">
+        <v>2215</v>
       </c>
       <c r="C528" s="2" t="str">
         <f>MID(D528,1,4)</f>
@@ -17146,8 +17146,8 @@
       <c r="A529" s="1">
         <v>40111100622</v>
       </c>
-      <c r="B529" t="e">
-        <v>#N/A</v>
+      <c r="B529" t="s">
+        <v>2215</v>
       </c>
       <c r="C529" s="2" t="str">
         <f>MID(D529,1,4)</f>
@@ -17161,8 +17161,8 @@
       <c r="A530" s="1">
         <v>40111100623</v>
       </c>
-      <c r="B530" t="e">
-        <v>#N/A</v>
+      <c r="B530" t="s">
+        <v>2215</v>
       </c>
       <c r="C530" s="2" t="str">
         <f>MID(D530,1,4)</f>
@@ -17224,8 +17224,8 @@
       <c r="A534" s="1">
         <v>40111100627</v>
       </c>
-      <c r="B534" t="e">
-        <v>#N/A</v>
+      <c r="B534" t="s">
+        <v>2215</v>
       </c>
       <c r="C534" s="2" t="str">
         <f>MID(D534,1,4)</f>
@@ -17267,8 +17267,8 @@
       <c r="A537" s="1">
         <v>40111100630</v>
       </c>
-      <c r="B537" t="e">
-        <v>#N/A</v>
+      <c r="B537" t="s">
+        <v>2215</v>
       </c>
       <c r="C537" s="2" t="str">
         <f>MID(D537,1,4)</f>
@@ -17282,8 +17282,8 @@
       <c r="A538" s="1">
         <v>40111100632</v>
       </c>
-      <c r="B538" t="e">
-        <v>#N/A</v>
+      <c r="B538" t="s">
+        <v>2215</v>
       </c>
       <c r="C538" s="2" t="str">
         <f>MID(D538,1,4)</f>
@@ -17311,8 +17311,8 @@
       <c r="A540" s="1">
         <v>40111100635</v>
       </c>
-      <c r="B540" t="e">
-        <v>#N/A</v>
+      <c r="B540" t="s">
+        <v>2215</v>
       </c>
       <c r="C540" s="2" t="str">
         <f>MID(D540,1,4)</f>
@@ -17371,8 +17371,8 @@
       <c r="A544" s="1">
         <v>40111100662</v>
       </c>
-      <c r="B544" t="e">
-        <v>#N/A</v>
+      <c r="B544" t="s">
+        <v>2215</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>2731</v>
@@ -17402,8 +17402,8 @@
       <c r="A546" s="1">
         <v>40111100664</v>
       </c>
-      <c r="B546" t="e">
-        <v>#N/A</v>
+      <c r="B546" t="s">
+        <v>2215</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>2732</v>
@@ -17416,8 +17416,8 @@
       <c r="A547" s="1">
         <v>40111100665</v>
       </c>
-      <c r="B547" t="e">
-        <v>#N/A</v>
+      <c r="B547" t="s">
+        <v>2215</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>2733</v>
@@ -17532,8 +17532,8 @@
       <c r="A554" s="1">
         <v>40111100684</v>
       </c>
-      <c r="B554" t="e">
-        <v>#N/A</v>
+      <c r="B554" t="s">
+        <v>2215</v>
       </c>
       <c r="C554" s="2" t="str">
         <f>MID(D554,1,7)</f>
@@ -41639,7 +41639,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A5:G1984" xr:uid="{7AACAD3D-2EDB-41A6-990A-3CFD850757FC}"/>
-  <conditionalFormatting sqref="C1866:C1876 C1:C1813 C1823:C1824 C1832 C1878:C1886 C1889:C1916 C1918:C1920 C1922:C1931 C1937 C1944 C1950:C1048576">
+  <conditionalFormatting sqref="C1866:C1876 C1:C62 C1823:C1824 C1832 C1878:C1886 C1889:C1916 C1918:C1920 C1922:C1931 C1937 C1944 C1950:C1048576 C64:C1813">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/codigos_ergopyme_homologacion.xlsx
+++ b/codigos_ergopyme_homologacion.xlsx
@@ -465,16 +465,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1989"/>
+  <dimension ref="A1:G1990"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="37.28515625" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
     <col width="48.42578125" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="6"/>
-    <col hidden="1" style="2" min="7" max="7"/>
-    <col hidden="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="5" max="6"/>
+    <col hidden="1" width="13" customWidth="1" style="2" min="7" max="7"/>
+    <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24342,7 +24342,7 @@
       </c>
       <c r="C1053" s="2" t="inlineStr">
         <is>
-          <t>677MYP085V2</t>
+          <t>677MYP085</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -24367,7 +24367,7 @@
       </c>
       <c r="C1054" s="2" t="inlineStr">
         <is>
-          <t>677MYP090V2</t>
+          <t>677MYP090</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -24392,7 +24392,7 @@
       </c>
       <c r="C1055" s="2" t="inlineStr">
         <is>
-          <t>677MYP095V2</t>
+          <t>677MYP095</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>677MYP165V2</t>
+          <t>677MYP165</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>677MYP175V2</t>
+          <t>677MYP175</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="C1067" s="2" t="inlineStr">
         <is>
-          <t>677MYP180V2</t>
+          <t>677MYP180</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="C1068" s="2" t="inlineStr">
         <is>
-          <t>677MYP185V2</t>
+          <t>677MYP185</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="C1069" s="2" t="inlineStr">
         <is>
-          <t>677MYP190V2</t>
+          <t>677MYP190</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>677MYP195V2</t>
+          <t>677MYP195</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="C1071" s="2" t="inlineStr">
         <is>
-          <t>677MYP200V2</t>
+          <t>677MYP200</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -24799,7 +24799,7 @@
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>677MYP205V2</t>
+          <t>677MYP205</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="C1073" s="2" t="inlineStr">
         <is>
-          <t>677MYP210V2</t>
+          <t>677MYP210</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
@@ -24849,7 +24849,7 @@
       </c>
       <c r="C1074" s="2" t="inlineStr">
         <is>
-          <t>677MYP215V2</t>
+          <t>677MYP215</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -24874,7 +24874,7 @@
       </c>
       <c r="C1075" s="2" t="inlineStr">
         <is>
-          <t>677MYP220V2</t>
+          <t>677MYP220</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C1076" s="2" t="inlineStr">
         <is>
-          <t>677MYP225V2</t>
+          <t>677MYP225</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="C1077" s="2" t="inlineStr">
         <is>
-          <t>677MYP230V2</t>
+          <t>677MYP230</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="C1078" s="2" t="inlineStr">
         <is>
-          <t>677MYP235V2</t>
+          <t>677MYP235</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="C1079" s="2" t="inlineStr">
         <is>
-          <t>677MYP240V2</t>
+          <t>677MYP240</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="C1080" s="2" t="inlineStr">
         <is>
-          <t>677MYP245V2</t>
+          <t>677MYP245</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
@@ -25024,7 +25024,7 @@
       </c>
       <c r="C1081" s="2" t="inlineStr">
         <is>
-          <t>677MYP250V2</t>
+          <t>677MYP250</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="C1082" s="2" t="inlineStr">
         <is>
-          <t>677MYP255V2</t>
+          <t>677MYP255</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="C1083" s="2" t="inlineStr">
         <is>
-          <t>677MYP260V2</t>
+          <t>677MYP260</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="C1084" s="2" t="inlineStr">
         <is>
-          <t>677MYP265V2</t>
+          <t>677MYP265</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="C1085" s="2" t="inlineStr">
         <is>
-          <t>677MYP270V2</t>
+          <t>677MYP270</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -25149,7 +25149,7 @@
       </c>
       <c r="C1086" s="2" t="inlineStr">
         <is>
-          <t>677MYP275V2</t>
+          <t>677MYP275</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -25174,7 +25174,7 @@
       </c>
       <c r="C1087" s="2" t="inlineStr">
         <is>
-          <t>677MYP280V2</t>
+          <t>677MYP280</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -25199,7 +25199,7 @@
       </c>
       <c r="C1088" s="2" t="inlineStr">
         <is>
-          <t>677MYP285V2</t>
+          <t>677MYP285</t>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
@@ -42281,7 +42281,7 @@
       </c>
       <c r="C1818" s="2" t="inlineStr">
         <is>
-          <t>677MTYP115PV2</t>
+          <t>677MTYP115P</t>
         </is>
       </c>
       <c r="D1818" t="inlineStr">
@@ -42697,7 +42697,7 @@
       </c>
       <c r="C1836" s="2" t="inlineStr">
         <is>
-          <t>677MTYP170AV2</t>
+          <t>677MTYP170A</t>
         </is>
       </c>
       <c r="D1836" t="inlineStr">
@@ -42722,7 +42722,7 @@
       </c>
       <c r="C1837" s="2" t="inlineStr">
         <is>
-          <t>677MTYP170PV2</t>
+          <t>677MTYP170P</t>
         </is>
       </c>
       <c r="D1837" t="inlineStr">
@@ -42772,7 +42772,7 @@
       </c>
       <c r="C1839" s="2" t="inlineStr">
         <is>
-          <t>677MTYP170CV2</t>
+          <t>677MTYP170C</t>
         </is>
       </c>
       <c r="D1839" t="inlineStr">
@@ -42843,7 +42843,7 @@
       </c>
       <c r="C1842" s="2" t="inlineStr">
         <is>
-          <t>677MTYP175AV2</t>
+          <t>677MTYP175A</t>
         </is>
       </c>
       <c r="D1842" t="inlineStr">
@@ -42868,7 +42868,7 @@
       </c>
       <c r="C1843" s="2" t="inlineStr">
         <is>
-          <t>677MTYP175PV2</t>
+          <t>677MTYP175P</t>
         </is>
       </c>
       <c r="D1843" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="C1844" s="2" t="inlineStr">
         <is>
-          <t>677MTYP175QV2</t>
+          <t>677MTYP175Q</t>
         </is>
       </c>
       <c r="D1844" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="C1845" s="2" t="inlineStr">
         <is>
-          <t>677MTYP175CV2</t>
+          <t>677MTYP175C</t>
         </is>
       </c>
       <c r="D1845" t="inlineStr">
@@ -42989,7 +42989,7 @@
       </c>
       <c r="C1848" s="2" t="inlineStr">
         <is>
-          <t>677MTYP180AV2</t>
+          <t>677MTYP180A</t>
         </is>
       </c>
       <c r="D1848" t="inlineStr">
@@ -43014,7 +43014,7 @@
       </c>
       <c r="C1849" s="2" t="inlineStr">
         <is>
-          <t>677MTYP180PV2</t>
+          <t>677MTYP180P</t>
         </is>
       </c>
       <c r="D1849" t="inlineStr">
@@ -43039,7 +43039,7 @@
       </c>
       <c r="C1850" s="2" t="inlineStr">
         <is>
-          <t>677MTYP180QV2</t>
+          <t>677MTYP180Q</t>
         </is>
       </c>
       <c r="D1850" t="inlineStr">
@@ -43064,7 +43064,7 @@
       </c>
       <c r="C1851" s="2" t="inlineStr">
         <is>
-          <t>677MTYP180CV2</t>
+          <t>677MTYP180C</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
@@ -43158,7 +43158,7 @@
       </c>
       <c r="C1855" s="2" t="inlineStr">
         <is>
-          <t>677MTYP185AV2</t>
+          <t>677MTYP185A</t>
         </is>
       </c>
       <c r="D1855" t="inlineStr">
@@ -43183,7 +43183,7 @@
       </c>
       <c r="C1856" s="2" t="inlineStr">
         <is>
-          <t>677MTYP185PV2</t>
+          <t>677MTYP185P</t>
         </is>
       </c>
       <c r="D1856" t="inlineStr">
@@ -43208,7 +43208,7 @@
       </c>
       <c r="C1857" s="2" t="inlineStr">
         <is>
-          <t>677MTYP185QV2</t>
+          <t>677MTYP185Q</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -43233,7 +43233,7 @@
       </c>
       <c r="C1858" s="2" t="inlineStr">
         <is>
-          <t>677MTYP185CV2</t>
+          <t>677MTYP185C</t>
         </is>
       </c>
       <c r="D1858" t="inlineStr">
@@ -43304,7 +43304,7 @@
       </c>
       <c r="C1861" s="2" t="inlineStr">
         <is>
-          <t>677MTYP190NV2</t>
+          <t>677MTYP190N</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -43329,7 +43329,7 @@
       </c>
       <c r="C1862" s="2" t="inlineStr">
         <is>
-          <t>677MTYP190AV2</t>
+          <t>677MTYP190A</t>
         </is>
       </c>
       <c r="D1862" t="inlineStr">
@@ -43354,7 +43354,7 @@
       </c>
       <c r="C1863" s="2" t="inlineStr">
         <is>
-          <t>677MTYP190PV2</t>
+          <t>677MTYP190P</t>
         </is>
       </c>
       <c r="D1863" t="inlineStr">
@@ -43379,7 +43379,7 @@
       </c>
       <c r="C1864" s="2" t="inlineStr">
         <is>
-          <t>677MTYP190QV2</t>
+          <t>677MTYP190Q</t>
         </is>
       </c>
       <c r="D1864" t="inlineStr">
@@ -43404,7 +43404,7 @@
       </c>
       <c r="C1865" s="2" t="inlineStr">
         <is>
-          <t>677MTYP190CV2</t>
+          <t>677MTYP190C</t>
         </is>
       </c>
       <c r="D1865" t="inlineStr">
@@ -43452,7 +43452,7 @@
       </c>
       <c r="C1867" s="2" t="inlineStr">
         <is>
-          <t>677MTYP195NV2</t>
+          <t>677MTYP195N</t>
         </is>
       </c>
       <c r="D1867" t="inlineStr">
@@ -43477,7 +43477,7 @@
       </c>
       <c r="C1868" s="2" t="inlineStr">
         <is>
-          <t>677MTYP195AV2</t>
+          <t>677MTYP195A</t>
         </is>
       </c>
       <c r="D1868" t="inlineStr">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C1869" s="2" t="inlineStr">
         <is>
-          <t>677MTYP195PV2</t>
+          <t>677MTYP195P</t>
         </is>
       </c>
       <c r="D1869" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="C1870" s="2" t="inlineStr">
         <is>
-          <t>677MTYP195QV2</t>
+          <t>677MTYP195Q</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
@@ -43552,7 +43552,7 @@
       </c>
       <c r="C1871" s="2" t="inlineStr">
         <is>
-          <t>677MTYP195CV2</t>
+          <t>677MTYP195C</t>
         </is>
       </c>
       <c r="D1871" t="inlineStr">
@@ -43623,7 +43623,7 @@
       </c>
       <c r="C1874" s="2" t="inlineStr">
         <is>
-          <t>677MTYP200NV2</t>
+          <t>677MTYP200N</t>
         </is>
       </c>
       <c r="D1874" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="C1876" s="2" t="inlineStr">
         <is>
-          <t>677MTYP200PV2</t>
+          <t>677MTYP200P</t>
         </is>
       </c>
       <c r="D1876" t="inlineStr">
@@ -43698,7 +43698,7 @@
       </c>
       <c r="C1877" s="2" t="inlineStr">
         <is>
-          <t>677MTYP200QV2</t>
+          <t>677MTYP200Q</t>
         </is>
       </c>
       <c r="D1877" t="inlineStr">
@@ -43723,7 +43723,7 @@
       </c>
       <c r="C1878" s="2" t="inlineStr">
         <is>
-          <t>677MTYP200CV2</t>
+          <t>677MTYP200C</t>
         </is>
       </c>
       <c r="D1878" t="inlineStr">
@@ -43748,7 +43748,7 @@
       </c>
       <c r="C1879" s="2" t="inlineStr">
         <is>
-          <t>677MTYP205NV2</t>
+          <t>677MTYP205N</t>
         </is>
       </c>
       <c r="D1879" t="inlineStr">
@@ -43773,7 +43773,7 @@
       </c>
       <c r="C1880" s="2" t="inlineStr">
         <is>
-          <t>677MTYP205AV2</t>
+          <t>677MTYP205A</t>
         </is>
       </c>
       <c r="D1880" t="inlineStr">
@@ -43798,7 +43798,7 @@
       </c>
       <c r="C1881" s="2" t="inlineStr">
         <is>
-          <t>677MTYP205PV2</t>
+          <t>677MTYP205P</t>
         </is>
       </c>
       <c r="D1881" t="inlineStr">
@@ -43823,7 +43823,7 @@
       </c>
       <c r="C1882" s="2" t="inlineStr">
         <is>
-          <t>677MTYP205QV2</t>
+          <t>677MTYP205Q</t>
         </is>
       </c>
       <c r="D1882" t="inlineStr">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="C1883" s="2" t="inlineStr">
         <is>
-          <t>677MTYP205CV2</t>
+          <t>677MTYP205C</t>
         </is>
       </c>
       <c r="D1883" t="inlineStr">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C1885" s="2" t="inlineStr">
         <is>
-          <t>677MTYP210NV2</t>
+          <t>677MTYP210N</t>
         </is>
       </c>
       <c r="D1885" t="inlineStr">
@@ -43921,7 +43921,7 @@
       </c>
       <c r="C1886" s="2" t="inlineStr">
         <is>
-          <t>677MTYP210AV2</t>
+          <t>677MTYP210A</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
@@ -43946,7 +43946,7 @@
       </c>
       <c r="C1887" s="2" t="inlineStr">
         <is>
-          <t>677MTYP210PV2</t>
+          <t>677MTYP210P</t>
         </is>
       </c>
       <c r="D1887" t="inlineStr">
@@ -43971,7 +43971,7 @@
       </c>
       <c r="C1888" s="2" t="inlineStr">
         <is>
-          <t>677MTYP210QV2</t>
+          <t>677MTYP210Q</t>
         </is>
       </c>
       <c r="D1888" t="inlineStr">
@@ -43996,7 +43996,7 @@
       </c>
       <c r="C1889" s="2" t="inlineStr">
         <is>
-          <t>677MTYP210CV2</t>
+          <t>677MTYP210C</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
@@ -44067,7 +44067,7 @@
       </c>
       <c r="C1892" s="2" t="inlineStr">
         <is>
-          <t>677MTYP215NV2</t>
+          <t>677MTYP215N</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
@@ -44092,7 +44092,7 @@
       </c>
       <c r="C1893" s="2" t="inlineStr">
         <is>
-          <t>677MTYP215AV2</t>
+          <t>677MTYP215A</t>
         </is>
       </c>
       <c r="D1893" t="inlineStr">
@@ -44117,7 +44117,7 @@
       </c>
       <c r="C1894" s="2" t="inlineStr">
         <is>
-          <t>677MTYP215PV2</t>
+          <t>677MTYP215P</t>
         </is>
       </c>
       <c r="D1894" t="inlineStr">
@@ -44142,7 +44142,7 @@
       </c>
       <c r="C1895" s="2" t="inlineStr">
         <is>
-          <t>677MTYP215QV2</t>
+          <t>677MTYP215Q</t>
         </is>
       </c>
       <c r="D1895" t="inlineStr">
@@ -44167,7 +44167,7 @@
       </c>
       <c r="C1896" s="2" t="inlineStr">
         <is>
-          <t>677MTYP215CV2</t>
+          <t>677MTYP215C</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
@@ -44238,7 +44238,7 @@
       </c>
       <c r="C1899" s="2" t="inlineStr">
         <is>
-          <t>677MTYP220NV2</t>
+          <t>677MTYP220N</t>
         </is>
       </c>
       <c r="D1899" t="inlineStr">
@@ -44263,7 +44263,7 @@
       </c>
       <c r="C1900" s="2" t="inlineStr">
         <is>
-          <t>677MTYP220AV2</t>
+          <t>677MTYP220A</t>
         </is>
       </c>
       <c r="D1900" t="inlineStr">
@@ -44288,7 +44288,7 @@
       </c>
       <c r="C1901" s="2" t="inlineStr">
         <is>
-          <t>677MTYP220PV2</t>
+          <t>677MTYP220P</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
@@ -44313,7 +44313,7 @@
       </c>
       <c r="C1902" s="2" t="inlineStr">
         <is>
-          <t>677MTYP220QV2</t>
+          <t>677MTYP220Q</t>
         </is>
       </c>
       <c r="D1902" t="inlineStr">
@@ -44338,7 +44338,7 @@
       </c>
       <c r="C1903" s="2" t="inlineStr">
         <is>
-          <t>677MTYP220CV2</t>
+          <t>677MTYP220C</t>
         </is>
       </c>
       <c r="D1903" t="inlineStr">
@@ -44432,7 +44432,7 @@
       </c>
       <c r="C1907" s="2" t="inlineStr">
         <is>
-          <t>677MTYP225NV2</t>
+          <t>677MTYP225N</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -44482,7 +44482,7 @@
       </c>
       <c r="C1909" s="2" t="inlineStr">
         <is>
-          <t>677MTYP225PV2</t>
+          <t>677MTYP225P</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
@@ -44507,7 +44507,7 @@
       </c>
       <c r="C1910" s="2" t="inlineStr">
         <is>
-          <t>677MTYP225QV2</t>
+          <t>677MTYP225Q</t>
         </is>
       </c>
       <c r="D1910" t="inlineStr">
@@ -44532,7 +44532,7 @@
       </c>
       <c r="C1911" s="2" t="inlineStr">
         <is>
-          <t>677MTYP225CV2</t>
+          <t>677MTYP225C</t>
         </is>
       </c>
       <c r="D1911" t="inlineStr">
@@ -44580,7 +44580,7 @@
       </c>
       <c r="C1913" s="2" t="inlineStr">
         <is>
-          <t>677MTYP230AV2</t>
+          <t>677MTYP230A</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
@@ -44605,7 +44605,7 @@
       </c>
       <c r="C1914" s="2" t="inlineStr">
         <is>
-          <t>677MTYP230PV2</t>
+          <t>677MTYP230P</t>
         </is>
       </c>
       <c r="D1914" t="inlineStr">
@@ -44630,7 +44630,7 @@
       </c>
       <c r="C1915" s="2" t="inlineStr">
         <is>
-          <t>677MTYP230QV2</t>
+          <t>677MTYP230Q</t>
         </is>
       </c>
       <c r="D1915" t="inlineStr">
@@ -44655,7 +44655,7 @@
       </c>
       <c r="C1916" s="2" t="inlineStr">
         <is>
-          <t>677MTYP230CV2</t>
+          <t>677MTYP230C</t>
         </is>
       </c>
       <c r="D1916" t="inlineStr">
@@ -44680,7 +44680,7 @@
       </c>
       <c r="C1917" s="2" t="inlineStr">
         <is>
-          <t>677MTYP235NV2</t>
+          <t>677MTYP235N</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
@@ -44728,7 +44728,7 @@
       </c>
       <c r="C1919" s="2" t="inlineStr">
         <is>
-          <t>677MTYP235PV2</t>
+          <t>677MTYP235P</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
@@ -44753,7 +44753,7 @@
       </c>
       <c r="C1920" s="2" t="inlineStr">
         <is>
-          <t>677MTYP235QV2</t>
+          <t>677MTYP235Q</t>
         </is>
       </c>
       <c r="D1920" t="inlineStr">
@@ -44778,7 +44778,7 @@
       </c>
       <c r="C1921" s="2" t="inlineStr">
         <is>
-          <t>677MTYP235CV2</t>
+          <t>677MTYP235C</t>
         </is>
       </c>
       <c r="D1921" t="inlineStr">
@@ -44849,7 +44849,7 @@
       </c>
       <c r="C1924" s="2" t="inlineStr">
         <is>
-          <t>677MTYP240NV2</t>
+          <t>677MTYP240N</t>
         </is>
       </c>
       <c r="D1924" t="inlineStr">
@@ -44874,7 +44874,7 @@
       </c>
       <c r="C1925" s="2" t="inlineStr">
         <is>
-          <t>677MTYP240AV2</t>
+          <t>677MTYP240A</t>
         </is>
       </c>
       <c r="D1925" t="inlineStr">
@@ -44899,7 +44899,7 @@
       </c>
       <c r="C1926" s="2" t="inlineStr">
         <is>
-          <t>677MTYP240PV2</t>
+          <t>677MTYP240P</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
@@ -44924,7 +44924,7 @@
       </c>
       <c r="C1927" s="2" t="inlineStr">
         <is>
-          <t>677MTYP240QV2</t>
+          <t>677MTYP240Q</t>
         </is>
       </c>
       <c r="D1927" t="inlineStr">
@@ -44949,7 +44949,7 @@
       </c>
       <c r="C1928" s="2" t="inlineStr">
         <is>
-          <t>677MTYP240CV2</t>
+          <t>677MTYP240C</t>
         </is>
       </c>
       <c r="D1928" t="inlineStr">
@@ -45066,7 +45066,7 @@
       </c>
       <c r="C1933" s="2" t="inlineStr">
         <is>
-          <t>677MTYP245NV2</t>
+          <t>677MTYP245N</t>
         </is>
       </c>
       <c r="D1933" t="inlineStr">
@@ -45091,7 +45091,7 @@
       </c>
       <c r="C1934" s="2" t="inlineStr">
         <is>
-          <t>677MTYP245AV2</t>
+          <t>677MTYP245A</t>
         </is>
       </c>
       <c r="D1934" t="inlineStr">
@@ -45116,7 +45116,7 @@
       </c>
       <c r="C1935" s="2" t="inlineStr">
         <is>
-          <t>677MTYP245PV2</t>
+          <t>677MTYP245P</t>
         </is>
       </c>
       <c r="D1935" t="inlineStr">
@@ -45141,7 +45141,7 @@
       </c>
       <c r="C1936" s="2" t="inlineStr">
         <is>
-          <t>677MTYP245QV2</t>
+          <t>677MTYP245Q</t>
         </is>
       </c>
       <c r="D1936" t="inlineStr">
@@ -45166,7 +45166,7 @@
       </c>
       <c r="C1937" s="2" t="inlineStr">
         <is>
-          <t>677MTYP245CV2</t>
+          <t>677MTYP245C</t>
         </is>
       </c>
       <c r="D1937" t="inlineStr">
@@ -45283,7 +45283,7 @@
       </c>
       <c r="C1942" s="2" t="inlineStr">
         <is>
-          <t>677MTYP250AV2</t>
+          <t>677MTYP250A</t>
         </is>
       </c>
       <c r="D1942" t="inlineStr">
@@ -45308,7 +45308,7 @@
       </c>
       <c r="C1943" s="2" t="inlineStr">
         <is>
-          <t>677MTYP250PV2</t>
+          <t>677MTYP250P</t>
         </is>
       </c>
       <c r="D1943" t="inlineStr">
@@ -45333,7 +45333,7 @@
       </c>
       <c r="C1944" s="2" t="inlineStr">
         <is>
-          <t>677MTYP250QV2</t>
+          <t>677MTYP250Q</t>
         </is>
       </c>
       <c r="D1944" t="inlineStr">
@@ -45358,7 +45358,7 @@
       </c>
       <c r="C1945" s="2" t="inlineStr">
         <is>
-          <t>677MTYP250CV2</t>
+          <t>677MTYP250C</t>
         </is>
       </c>
       <c r="D1945" t="inlineStr">
@@ -45406,7 +45406,7 @@
       </c>
       <c r="C1947" s="2" t="inlineStr">
         <is>
-          <t>677MTYP255AV2</t>
+          <t>677MTYP255A</t>
         </is>
       </c>
       <c r="D1947" t="inlineStr">
@@ -45431,7 +45431,7 @@
       </c>
       <c r="C1948" s="2" t="inlineStr">
         <is>
-          <t>677MTYP255PV2</t>
+          <t>677MTYP255P</t>
         </is>
       </c>
       <c r="D1948" t="inlineStr">
@@ -45456,7 +45456,7 @@
       </c>
       <c r="C1949" s="2" t="inlineStr">
         <is>
-          <t>677MTYP255QV2</t>
+          <t>677MTYP255Q</t>
         </is>
       </c>
       <c r="D1949" t="inlineStr">
@@ -45481,7 +45481,7 @@
       </c>
       <c r="C1950" s="2" t="inlineStr">
         <is>
-          <t>677MTYP255CV2</t>
+          <t>677MTYP255C</t>
         </is>
       </c>
       <c r="D1950" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="C1951" s="2" t="inlineStr">
         <is>
-          <t>677MTYP260NV2</t>
+          <t>677MTYP260N</t>
         </is>
       </c>
       <c r="D1951" t="inlineStr">
@@ -45531,7 +45531,7 @@
       </c>
       <c r="C1952" s="2" t="inlineStr">
         <is>
-          <t>677MTYP260AV2</t>
+          <t>677MTYP260A</t>
         </is>
       </c>
       <c r="D1952" t="inlineStr">
@@ -45579,7 +45579,7 @@
       </c>
       <c r="C1954" s="2" t="inlineStr">
         <is>
-          <t>677MTYP260QV2</t>
+          <t>677MTYP260Q</t>
         </is>
       </c>
       <c r="D1954" t="inlineStr">
@@ -45604,7 +45604,7 @@
       </c>
       <c r="C1955" s="2" t="inlineStr">
         <is>
-          <t>677MTYP260CV2</t>
+          <t>677MTYP260C</t>
         </is>
       </c>
       <c r="D1955" t="inlineStr">
@@ -45629,7 +45629,7 @@
       </c>
       <c r="C1956" s="2" t="inlineStr">
         <is>
-          <t>677MTYP265NV2</t>
+          <t>677MTYP265N</t>
         </is>
       </c>
       <c r="D1956" t="inlineStr">
@@ -45654,7 +45654,7 @@
       </c>
       <c r="C1957" s="2" t="inlineStr">
         <is>
-          <t>677MTYP265AV2</t>
+          <t>677MTYP265A</t>
         </is>
       </c>
       <c r="D1957" t="inlineStr">
@@ -45679,7 +45679,7 @@
       </c>
       <c r="C1958" s="2" t="inlineStr">
         <is>
-          <t>677MTYP265PV2</t>
+          <t>677MTYP265P</t>
         </is>
       </c>
       <c r="D1958" t="inlineStr">
@@ -45704,7 +45704,7 @@
       </c>
       <c r="C1959" s="2" t="inlineStr">
         <is>
-          <t>677MTYP265QV2</t>
+          <t>677MTYP265Q</t>
         </is>
       </c>
       <c r="D1959" t="inlineStr">
@@ -45729,7 +45729,7 @@
       </c>
       <c r="C1960" s="2" t="inlineStr">
         <is>
-          <t>677MTYP265CV2</t>
+          <t>677MTYP265C</t>
         </is>
       </c>
       <c r="D1960" t="inlineStr">
@@ -45754,7 +45754,7 @@
       </c>
       <c r="C1961" s="2" t="inlineStr">
         <is>
-          <t>677MTYP270NV2</t>
+          <t>677MTYP270N</t>
         </is>
       </c>
       <c r="D1961" t="inlineStr">
@@ -45779,7 +45779,7 @@
       </c>
       <c r="C1962" s="2" t="inlineStr">
         <is>
-          <t>677MTYP270AV2</t>
+          <t>677MTYP270A</t>
         </is>
       </c>
       <c r="D1962" t="inlineStr">
@@ -45804,7 +45804,7 @@
       </c>
       <c r="C1963" s="2" t="inlineStr">
         <is>
-          <t>677MTYP270PV2</t>
+          <t>677MTYP270P</t>
         </is>
       </c>
       <c r="D1963" t="inlineStr">
@@ -45829,7 +45829,7 @@
       </c>
       <c r="C1964" s="2" t="inlineStr">
         <is>
-          <t>677MTYP270QV2</t>
+          <t>677MTYP270Q</t>
         </is>
       </c>
       <c r="D1964" t="inlineStr">
@@ -45854,7 +45854,7 @@
       </c>
       <c r="C1965" s="2" t="inlineStr">
         <is>
-          <t>677MTYP270CV2</t>
+          <t>677MTYP270C</t>
         </is>
       </c>
       <c r="D1965" t="inlineStr">
@@ -45925,7 +45925,7 @@
       </c>
       <c r="C1968" s="2" t="inlineStr">
         <is>
-          <t>677MTYP275PV2</t>
+          <t>677MTYP275P</t>
         </is>
       </c>
       <c r="D1968" t="inlineStr">
@@ -45950,7 +45950,7 @@
       </c>
       <c r="C1969" s="2" t="inlineStr">
         <is>
-          <t>677MTYP275QV2</t>
+          <t>677MTYP275Q</t>
         </is>
       </c>
       <c r="D1969" t="inlineStr">
@@ -45975,7 +45975,7 @@
       </c>
       <c r="C1970" s="2" t="inlineStr">
         <is>
-          <t>677MTYP275CV2</t>
+          <t>677MTYP275C</t>
         </is>
       </c>
       <c r="D1970" t="inlineStr">
@@ -46000,7 +46000,7 @@
       </c>
       <c r="C1971" s="2" t="inlineStr">
         <is>
-          <t>677MTYP280NV2</t>
+          <t>677MTYP280N</t>
         </is>
       </c>
       <c r="D1971" t="inlineStr">
@@ -46025,7 +46025,7 @@
       </c>
       <c r="C1972" s="2" t="inlineStr">
         <is>
-          <t>677MTYP280AV2</t>
+          <t>677MTYP280A</t>
         </is>
       </c>
       <c r="D1972" t="inlineStr">
@@ -46050,7 +46050,7 @@
       </c>
       <c r="C1973" s="2" t="inlineStr">
         <is>
-          <t>677MTYP280PV2</t>
+          <t>677MTYP280P</t>
         </is>
       </c>
       <c r="D1973" t="inlineStr">
@@ -46075,7 +46075,7 @@
       </c>
       <c r="C1974" s="2" t="inlineStr">
         <is>
-          <t>677MTYP280QV2</t>
+          <t>677MTYP280Q</t>
         </is>
       </c>
       <c r="D1974" t="inlineStr">
@@ -46100,7 +46100,7 @@
       </c>
       <c r="C1975" s="2" t="inlineStr">
         <is>
-          <t>677MTYP280CV2</t>
+          <t>677MTYP280C</t>
         </is>
       </c>
       <c r="D1975" t="inlineStr">
@@ -46125,7 +46125,7 @@
       </c>
       <c r="C1976" s="2" t="inlineStr">
         <is>
-          <t>677MTYP285NV2</t>
+          <t>677MTYP285N</t>
         </is>
       </c>
       <c r="D1976" t="inlineStr">
@@ -46150,7 +46150,7 @@
       </c>
       <c r="C1977" s="2" t="inlineStr">
         <is>
-          <t>677MTYP285AV2</t>
+          <t>677MTYP285A</t>
         </is>
       </c>
       <c r="D1977" t="inlineStr">
@@ -46175,7 +46175,7 @@
       </c>
       <c r="C1978" s="2" t="inlineStr">
         <is>
-          <t>677MTYP285PV2</t>
+          <t>677MTYP285P</t>
         </is>
       </c>
       <c r="D1978" t="inlineStr">
@@ -46200,7 +46200,7 @@
       </c>
       <c r="C1979" s="2" t="inlineStr">
         <is>
-          <t>677MTYP285QV2</t>
+          <t>677MTYP285Q</t>
         </is>
       </c>
       <c r="D1979" t="inlineStr">
@@ -46225,7 +46225,7 @@
       </c>
       <c r="C1980" s="2" t="inlineStr">
         <is>
-          <t>677MTYP285CV2</t>
+          <t>677MTYP285C</t>
         </is>
       </c>
       <c r="D1980" t="inlineStr">
@@ -46428,6 +46428,26 @@
       <c r="D1989" t="inlineStr">
         <is>
           <t>BI-FLEX T MONOFOCAL TORIC 34.0 CYL 2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="n">
+        <v>4010210026</v>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>MEDICONTUR</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>VISCO BIOVIS 3.0</t>
+        </is>
+      </c>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>VISCO BIOVIS 3.0</t>
         </is>
       </c>
     </row>

--- a/codigos_ergopyme_homologacion.xlsx
+++ b/codigos_ergopyme_homologacion.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1990"/>
+  <dimension ref="A1:G1996"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -26146,7 +26146,7 @@
       </c>
       <c r="C1127" s="2" t="inlineStr">
         <is>
-          <t>677ADYP550</t>
+          <t>677ADYP560</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -46448,6 +46448,126 @@
       <c r="D1990" t="inlineStr">
         <is>
           <t>VISCO BIOVIS 3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="n">
+        <v>20102114010300</v>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>MEDICONTUR</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45DT -01.0 CYL 3.00 D</t>
+        </is>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45DT -01.0 CYL 3.00 D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="n">
+        <v>20102201000001</v>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>MEDICONTUR</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>BASIS Z TRIFOCAL 690MY</t>
+        </is>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>BASIS Z TRIFOCAL 690MY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="n">
+        <v>20102201000002</v>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>MEDICONTUR</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>BASIS Z ASPHERIC PRELOADED 860PAY</t>
+        </is>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>BASIS Z ASPHERIC PRELOADED 860PAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="n">
+        <v>20102201000003</v>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>MEDICONTUR</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>BASIS Z EDOF PRELOADED 860PEY</t>
+        </is>
+      </c>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>BASIS Z EDOF PRELOADED 860PEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="n">
+        <v>20102201000004</v>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>MEDICONTUR</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45RD2</t>
+        </is>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45RD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="n">
+        <v>20102201000010</v>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>MEDICONTUR</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45DT -3.00 CYL 3.00</t>
+        </is>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>1STQ ADDON A45DT -3.00 CYL 3.00</t>
         </is>
       </c>
     </row>

--- a/codigos_ergopyme_homologacion.xlsx
+++ b/codigos_ergopyme_homologacion.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1996"/>
+  <dimension ref="A1:G1998"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -46571,6 +46571,46 @@
         </is>
       </c>
     </row>
+    <row r="1997">
+      <c r="A1997" t="n">
+        <v>20102201000005</v>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>MEDICONTUR</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>MEDJET 2.2 MA</t>
+        </is>
+      </c>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>MEDJET 2.2 MA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="n">
+        <v>4010101012</v>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>BVI PHYSIOL</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>INYECTOR 2,0</t>
+        </is>
+      </c>
+      <c r="D1998" t="inlineStr">
+        <is>
+          <t>INYECTOR 2,0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A5:G1984"/>
   <conditionalFormatting sqref="C1:C62 C64:C1813 C1823:C1824 C1832 C1866:C1876 C1878:C1886 C1889:C1916 C1918:C1920 C1922:C1931 C1937 C1944 C1950:C1048576">
